--- a/tame_output/ON/bt/strategyON_20231210.xlsx
+++ b/tame_output/ON/bt/strategyON_20231210.xlsx
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-70.9%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-36.7%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.912903254947839</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -41967,7 +41967,7 @@
         <v>45221</v>
       </c>
       <c r="B1759" t="n">
-        <v>2.94063219676755</v>
+        <v>2.940632196767551</v>
       </c>
       <c r="C1759" t="n">
         <v>2.964689051375926</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055148</v>
+        <v>3.048806209055149</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42105,7 +42105,7 @@
         <v>45227</v>
       </c>
       <c r="B1765" t="n">
-        <v>3.046605534538362</v>
+        <v>3.046605534538361</v>
       </c>
       <c r="C1765" t="n">
         <v>3.030564355893199</v>
@@ -42151,7 +42151,7 @@
         <v>45229</v>
       </c>
       <c r="B1767" t="n">
-        <v>3.053640504831979</v>
+        <v>3.053640504831978</v>
       </c>
       <c r="C1767" t="n">
         <v>3.033268356072139</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714844</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963481</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583696</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742726</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589526</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872959</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946331</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336487</v>
+        <v>3.300520058336486</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43071,22 +43071,22 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>2.994653036913648</v>
+        <v>2.994653036913647</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>0.7171552114066975</v>
+        <v>0.7148386162932265</v>
       </c>
       <c r="E1807" t="n">
-        <v>3.379881808327389</v>
+        <v>3.378955170282</v>
       </c>
       <c r="F1807" t="n">
-        <v>1.728019917566921</v>
+        <v>1.72570332245345</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.130188098618611</v>
+        <v>4.128798141550528</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231210.xlsx
+++ b/tame_output/ON/bt/strategyON_20231210.xlsx
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-70.7%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-36.7%</t>
+          <t>-36.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>111.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.91290325494784</v>
+        <v>2.912903254947839</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -41967,7 +41967,7 @@
         <v>45221</v>
       </c>
       <c r="B1759" t="n">
-        <v>2.940632196767551</v>
+        <v>2.94063219676755</v>
       </c>
       <c r="C1759" t="n">
         <v>2.964689051375926</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055149</v>
+        <v>3.048806209055148</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42105,7 +42105,7 @@
         <v>45227</v>
       </c>
       <c r="B1765" t="n">
-        <v>3.046605534538361</v>
+        <v>3.046605534538362</v>
       </c>
       <c r="C1765" t="n">
         <v>3.030564355893199</v>
@@ -42151,7 +42151,7 @@
         <v>45229</v>
       </c>
       <c r="B1767" t="n">
-        <v>3.053640504831978</v>
+        <v>3.053640504831979</v>
       </c>
       <c r="C1767" t="n">
         <v>3.033268356072139</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714844</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.18551435596348</v>
+        <v>3.185514355963481</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583695</v>
+        <v>3.199276732583696</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742725</v>
+        <v>3.238767863742726</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589525</v>
+        <v>3.260068416589526</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872958</v>
+        <v>3.306739876872959</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.31216459594633</v>
+        <v>3.312164595946331</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336486</v>
+        <v>3.300520058336487</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43071,22 +43071,22 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>2.994653036913647</v>
+        <v>2.994653036913648</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>0.7148386162932265</v>
+        <v>0.7172834300744684</v>
       </c>
       <c r="E1807" t="n">
-        <v>3.378955170282</v>
+        <v>3.379933095794497</v>
       </c>
       <c r="F1807" t="n">
-        <v>1.72570332245345</v>
+        <v>1.728148136234692</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.128798141550528</v>
+        <v>4.130265029819274</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231210.xlsx
+++ b/tame_output/ON/bt/strategyON_20231210.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>479.9%</t>
+          <t>477.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-97.3%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,27 +1145,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-15.1%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,32 +1293,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>44.3%</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>32.6%</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.9%</t>
+          <t>102.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-14.0%</t>
         </is>
       </c>
     </row>
@@ -41967,7 +41967,7 @@
         <v>45221</v>
       </c>
       <c r="B1759" t="n">
-        <v>2.94063219676755</v>
+        <v>2.940632196767551</v>
       </c>
       <c r="C1759" t="n">
         <v>2.964689051375926</v>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055148</v>
+        <v>3.048806209055149</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42105,7 +42105,7 @@
         <v>45227</v>
       </c>
       <c r="B1765" t="n">
-        <v>3.046605534538362</v>
+        <v>3.046605534538361</v>
       </c>
       <c r="C1765" t="n">
         <v>3.030564355893199</v>
@@ -42151,7 +42151,7 @@
         <v>45229</v>
       </c>
       <c r="B1767" t="n">
-        <v>3.053640504831979</v>
+        <v>3.053640504831978</v>
       </c>
       <c r="C1767" t="n">
         <v>3.033268356072139</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.06824651857159</v>
+        <v>3.068246518571589</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066013</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293022</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239775</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597767</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527686</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487809</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823381</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714842</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083877</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666734</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097099</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762259</v>
+        <v>3.169279212762258</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963481</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583696</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742726</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589526</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872959</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946331</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336487</v>
+        <v>3.300520058336486</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43071,22 +43071,22 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>2.994653036913648</v>
+        <v>2.994653036913647</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>0.7172834300744684</v>
+        <v>0.4511650853480568</v>
       </c>
       <c r="E1807" t="n">
-        <v>3.379933095794497</v>
+        <v>3.273485757903932</v>
       </c>
       <c r="F1807" t="n">
-        <v>1.728148136234692</v>
+        <v>1.46202979150828</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.130265029819274</v>
+        <v>3.970594022983427</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231210.xlsx
+++ b/tame_output/ON/bt/strategyON_20231210.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-307.3%</t>
+          <t>-342.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,32 +977,32 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>477.1%</t>
+          <t>475.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-136.3%</t>
+          <t>-161.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-97.3%</t>
+          <t>-106.8%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-111.4%</t>
+          <t>-125.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-18.9%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-113.2%</t>
+          <t>-135.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1283,27 +1283,27 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.0%</t>
+          <t>-159.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-59.7%</t>
         </is>
       </c>
     </row>
@@ -1365,17 +1365,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,15 +1413,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-56.4%</t>
+          <t>-70.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,32 +1451,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>102.9%</t>
+          <t>105.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-12.0%</t>
         </is>
       </c>
     </row>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.912903254947839</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -41973,16 +41973,16 @@
         <v>2.964689051375926</v>
       </c>
       <c r="D1759" t="n">
-        <v>-1.471036665324345</v>
+        <v>-1.826225702149536</v>
       </c>
       <c r="E1759" t="n">
-        <v>2.375917960932441</v>
+        <v>2.233842346202365</v>
       </c>
       <c r="F1759" t="n">
-        <v>1.039171953711096</v>
+        <v>0.8130998247229593</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.588192223602586</v>
+        <v>3.452548946209703</v>
       </c>
     </row>
     <row r="1760">
@@ -41996,16 +41996,16 @@
         <v>2.992474709334104</v>
       </c>
       <c r="D1760" t="n">
-        <v>-1.519279314210056</v>
+        <v>-1.874468351035248</v>
       </c>
       <c r="E1760" t="n">
-        <v>2.384406559336334</v>
+        <v>2.242330944606258</v>
       </c>
       <c r="F1760" t="n">
-        <v>1.039171953711096</v>
+        <v>0.8130998247229593</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.615977881560763</v>
+        <v>3.480334604167881</v>
       </c>
     </row>
     <row r="1761">
@@ -42019,16 +42019,16 @@
         <v>3.010249418375564</v>
       </c>
       <c r="D1761" t="n">
-        <v>-1.512181313242555</v>
+        <v>-1.867370350067746</v>
       </c>
       <c r="E1761" t="n">
-        <v>2.405020468764795</v>
+        <v>2.262944854034719</v>
       </c>
       <c r="F1761" t="n">
-        <v>1.039279151822472</v>
+        <v>0.8132070228343352</v>
       </c>
       <c r="G1761" t="n">
-        <v>3.633816909469049</v>
+        <v>3.498173632076167</v>
       </c>
     </row>
     <row r="1762">
@@ -42042,16 +42042,16 @@
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>-1.510978246946448</v>
+        <v>-1.86616728377164</v>
       </c>
       <c r="E1762" t="n">
-        <v>2.405975254964278</v>
+        <v>2.263899640234202</v>
       </c>
       <c r="F1762" t="n">
-        <v>1.039279151822472</v>
+        <v>0.8132070228343352</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.634290469150089</v>
+        <v>3.498647191757208</v>
       </c>
     </row>
     <row r="1763">
@@ -42065,16 +42065,16 @@
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>-1.508625199613203</v>
+        <v>-1.863814236438395</v>
       </c>
       <c r="E1763" t="n">
-        <v>2.412255846034474</v>
+        <v>2.270180231304397</v>
       </c>
       <c r="F1763" t="n">
-        <v>1.041632199155718</v>
+        <v>0.8155600701675807</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.641041669686934</v>
+        <v>3.505398392294051</v>
       </c>
     </row>
     <row r="1764">
@@ -42088,16 +42088,16 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>-1.507508917621977</v>
+        <v>-1.862697954447168</v>
       </c>
       <c r="E1764" t="n">
-        <v>2.427279383667014</v>
+        <v>2.285203768936937</v>
       </c>
       <c r="F1764" t="n">
-        <v>1.042748481146944</v>
+        <v>0.8166763521588069</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.656288463717719</v>
+        <v>3.520645186324837</v>
       </c>
     </row>
     <row r="1765">
@@ -42111,16 +42111,16 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>-1.503770961560922</v>
+        <v>-1.858959998386113</v>
       </c>
       <c r="E1765" t="n">
-        <v>2.428699546955083</v>
+        <v>2.286623932225007</v>
       </c>
       <c r="F1765" t="n">
-        <v>1.045124933427569</v>
+        <v>0.8190528044394316</v>
       </c>
       <c r="G1765" t="n">
-        <v>3.657639315949741</v>
+        <v>3.521996038556859</v>
       </c>
     </row>
     <row r="1766">
@@ -42134,16 +42134,16 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>-1.495273815899788</v>
+        <v>-1.85046285272498</v>
       </c>
       <c r="E1766" t="n">
-        <v>2.430413829717631</v>
+        <v>2.288338214987554</v>
       </c>
       <c r="F1766" t="n">
-        <v>1.045124933427569</v>
+        <v>0.8190528044394316</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.655954740447835</v>
+        <v>3.520311463054953</v>
       </c>
     </row>
     <row r="1767">
@@ -42157,16 +42157,16 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-1.494965855815064</v>
+        <v>-1.850154892640255</v>
       </c>
       <c r="E1767" t="n">
-        <v>2.434925589432367</v>
+        <v>2.29284997470229</v>
       </c>
       <c r="F1767" t="n">
-        <v>1.046306647520268</v>
+        <v>0.8202345185321317</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.661052344584302</v>
+        <v>3.52540906719142</v>
       </c>
     </row>
     <row r="1768">
@@ -42180,16 +42180,16 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-1.493184093444472</v>
+        <v>-1.848373130269664</v>
       </c>
       <c r="E1768" t="n">
-        <v>2.437298591557477</v>
+        <v>2.295222976827401</v>
       </c>
       <c r="F1768" t="n">
-        <v>1.046306647520268</v>
+        <v>0.8202345185321317</v>
       </c>
       <c r="G1768" t="n">
-        <v>3.662712641761176</v>
+        <v>3.527069364368294</v>
       </c>
     </row>
     <row r="1769">
@@ -42203,16 +42203,16 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-1.497261448581564</v>
+        <v>-1.852450485406755</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.450701819766331</v>
+        <v>2.308626205036254</v>
       </c>
       <c r="F1769" t="n">
-        <v>1.046306647520268</v>
+        <v>0.8202345185321317</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.677746812024866</v>
+        <v>3.542103534631984</v>
       </c>
     </row>
     <row r="1770">
@@ -42226,16 +42226,16 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-1.487269367655155</v>
+        <v>-1.842458404480346</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.453013086801028</v>
+        <v>2.310937472070952</v>
       </c>
       <c r="F1770" t="n">
-        <v>1.056298728446678</v>
+        <v>0.8302265994585408</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.682056495244845</v>
+        <v>3.546413217851963</v>
       </c>
     </row>
     <row r="1771">
@@ -42249,16 +42249,16 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-1.487825122711192</v>
+        <v>-1.843014159536384</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.455692594675204</v>
+        <v>2.313616979945128</v>
       </c>
       <c r="F1771" t="n">
-        <v>1.0546913146856</v>
+        <v>0.828619185697463</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.683993856884789</v>
+        <v>3.548350579491907</v>
       </c>
     </row>
     <row r="1772">
@@ -42272,16 +42272,16 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-1.491039475124504</v>
+        <v>-1.846228511949696</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.459931842849027</v>
+        <v>2.31785622811895</v>
       </c>
       <c r="F1772" t="n">
-        <v>1.0546913146856</v>
+        <v>0.828619185697463</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.689518846023936</v>
+        <v>3.553875568631054</v>
       </c>
     </row>
     <row r="1773">
@@ -42295,16 +42295,16 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-1.508047720527113</v>
+        <v>-1.863236757352305</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.454206117325714</v>
+        <v>2.312130502595637</v>
       </c>
       <c r="F1773" t="n">
-        <v>1.057690449698574</v>
+        <v>0.8316183207104367</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.692395899669452</v>
+        <v>3.55675262227657</v>
       </c>
     </row>
     <row r="1774">
@@ -42318,16 +42318,16 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-1.489087998075759</v>
+        <v>-1.84427703490095</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.462539868477529</v>
+        <v>2.320464253747452</v>
       </c>
       <c r="F1774" t="n">
-        <v>1.057690449698574</v>
+        <v>0.8316183207104367</v>
       </c>
       <c r="G1774" t="n">
-        <v>3.693145761840725</v>
+        <v>3.557502484447843</v>
       </c>
     </row>
     <row r="1775">
@@ -42341,16 +42341,16 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-1.48785327347295</v>
+        <v>-1.843042310298141</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.461269355782234</v>
+        <v>2.319193741052157</v>
       </c>
       <c r="F1775" t="n">
-        <v>1.057690449698574</v>
+        <v>0.8316183207104367</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.691381359304306</v>
+        <v>3.555738081911424</v>
       </c>
     </row>
     <row r="1776">
@@ -42364,16 +42364,16 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-1.497887537296599</v>
+        <v>-1.85307657412179</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.460823260089636</v>
+        <v>2.318747645359559</v>
       </c>
       <c r="F1776" t="n">
-        <v>1.057690449698574</v>
+        <v>0.8316183207104367</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.694948969141168</v>
+        <v>3.559305691748286</v>
       </c>
     </row>
     <row r="1777">
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-1.502926535594465</v>
+        <v>-1.858115572419657</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.482789622660098</v>
+        <v>2.340714007930022</v>
       </c>
       <c r="F1777" t="n">
-        <v>1.052651451400707</v>
+        <v>0.8265793224125699</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.715907532052057</v>
+        <v>3.580264254659175</v>
       </c>
     </row>
     <row r="1778">
@@ -42410,16 +42410,16 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-1.493106817433915</v>
+        <v>-1.848295854259106</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.484186221411548</v>
+        <v>2.342110606681471</v>
       </c>
       <c r="F1778" t="n">
-        <v>1.059081391617394</v>
+        <v>0.8330092626292573</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.717234207669299</v>
+        <v>3.581590930276417</v>
       </c>
     </row>
     <row r="1779">
@@ -42433,16 +42433,16 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-1.491305190594961</v>
+        <v>-1.846494227420152</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.470155434150755</v>
+        <v>2.328079819420679</v>
       </c>
       <c r="F1779" t="n">
-        <v>1.059081391617394</v>
+        <v>0.8330092626292573</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.702482769672925</v>
+        <v>3.566839492280042</v>
       </c>
     </row>
     <row r="1780">
@@ -42456,16 +42456,16 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-1.490316508850793</v>
+        <v>-1.845505545675984</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.468664663164095</v>
+        <v>2.326589048434018</v>
       </c>
       <c r="F1780" t="n">
-        <v>1.059081391617394</v>
+        <v>0.8330092626292573</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.700596525988597</v>
+        <v>3.564953248595715</v>
       </c>
     </row>
     <row r="1781">
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-1.482320154329254</v>
+        <v>-1.837509191154446</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.47383683142855</v>
+        <v>2.331761216698474</v>
       </c>
       <c r="F1781" t="n">
-        <v>1.067077746138933</v>
+        <v>0.8410056171507959</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.70736796515736</v>
+        <v>3.571724687764478</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-1.477336403657345</v>
+        <v>-1.832525440482537</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.487668912288226</v>
+        <v>2.345593297558149</v>
       </c>
       <c r="F1782" t="n">
-        <v>1.072061496810842</v>
+        <v>0.8459893678227046</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.722196796151417</v>
+        <v>3.586553518758535</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-1.47095026470779</v>
+        <v>-1.826139301532981</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.496951570879837</v>
+        <v>2.35487595614976</v>
       </c>
       <c r="F1783" t="n">
-        <v>1.072061496810842</v>
+        <v>0.8459893678227046</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.728924999163206</v>
+        <v>3.593281721770324</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-1.482755615026423</v>
+        <v>-1.837944651851614</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.496245519511926</v>
+        <v>2.35416990478185</v>
       </c>
       <c r="F1784" t="n">
-        <v>1.060256146492209</v>
+        <v>0.834184017504072</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.725857877731569</v>
+        <v>3.590214600338687</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-1.474023804247756</v>
+        <v>-1.829212841072948</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.505685701433282</v>
+        <v>2.363610086703205</v>
       </c>
       <c r="F1785" t="n">
-        <v>1.068987957270875</v>
+        <v>0.8429158282827383</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.737044421808658</v>
+        <v>3.601401144415776</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-1.467686917603304</v>
+        <v>-1.822875954428496</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.503531275039048</v>
+        <v>2.361455660308972</v>
       </c>
       <c r="F1786" t="n">
-        <v>1.068987957270875</v>
+        <v>0.8429158282827383</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.732355240756644</v>
+        <v>3.596711963363762</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-1.465152469875936</v>
+        <v>-1.820341506701127</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.514507711932189</v>
+        <v>2.372432097202113</v>
       </c>
       <c r="F1787" t="n">
-        <v>1.068987957270875</v>
+        <v>0.8429158282827383</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.742317898558837</v>
+        <v>3.606674621165955</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-1.46522836885654</v>
+        <v>-1.820417405681732</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.506892032532857</v>
+        <v>2.364816417802781</v>
       </c>
       <c r="F1788" t="n">
-        <v>1.069751217960202</v>
+        <v>0.8436790889720651</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.735190535165343</v>
+        <v>3.599547257772461</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-1.475730558415887</v>
+        <v>-1.830919595241079</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.480455732499492</v>
+        <v>2.338380117769415</v>
       </c>
       <c r="F1789" t="n">
-        <v>1.059249028400855</v>
+        <v>0.8331768994127184</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.706653797220108</v>
+        <v>3.571010519827226</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-1.477563821095003</v>
+        <v>-1.832752857920195</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.480423267273967</v>
+        <v>2.338347652543891</v>
       </c>
       <c r="F1790" t="n">
-        <v>1.059249028400855</v>
+        <v>0.8331768994127184</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.70735463706623</v>
+        <v>3.571711359673348</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-1.482572936156587</v>
+        <v>-1.837761972981779</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.478936701078193</v>
+        <v>2.336861086348117</v>
       </c>
       <c r="F1791" t="n">
-        <v>1.058254450842321</v>
+        <v>0.8321823218541837</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.707274970359969</v>
+        <v>3.571631692967086</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-1.486278492793402</v>
+        <v>-1.841467529618593</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.476682203663832</v>
+        <v>2.334606588933756</v>
       </c>
       <c r="F1792" t="n">
-        <v>1.056384775584686</v>
+        <v>0.8303126465965488</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.705380890445753</v>
+        <v>3.569737613052871</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-1.485046167436036</v>
+        <v>-1.840235204261228</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.477594985869098</v>
+        <v>2.335519371139021</v>
       </c>
       <c r="F1793" t="n">
-        <v>1.057015151956723</v>
+        <v>0.8309430229685864</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.706178968331295</v>
+        <v>3.570535690938413</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-1.474718170420184</v>
+        <v>-1.829907207245376</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.485856092839652</v>
+        <v>2.343780478109576</v>
       </c>
       <c r="F1794" t="n">
-        <v>1.067343148972576</v>
+        <v>0.8412710199844385</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.71650567470502</v>
+        <v>3.580862397312138</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-1.474601835272628</v>
+        <v>-1.82979087209782</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.492423287100511</v>
+        <v>2.350347672370435</v>
       </c>
       <c r="F1795" t="n">
-        <v>1.067459484120131</v>
+        <v>0.8413873551319943</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.72309613599539</v>
+        <v>3.587452858602508</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-1.476447244849496</v>
+        <v>-1.831636281674688</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.488659093715153</v>
+        <v>2.346583478985076</v>
       </c>
       <c r="F1796" t="n">
-        <v>1.067459484120131</v>
+        <v>0.8413873551319943</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.720070106440779</v>
+        <v>3.584426829047896</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-1.474948812324397</v>
+        <v>-1.830137849149589</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.489196754586326</v>
+        <v>2.347121139856249</v>
       </c>
       <c r="F1797" t="n">
-        <v>1.06895791664523</v>
+        <v>0.8428857876570932</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.720907453816971</v>
+        <v>3.585264176424089</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-1.483013064517131</v>
+        <v>-1.838202101342323</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.487249031652544</v>
+        <v>2.345173416922467</v>
       </c>
       <c r="F1798" t="n">
-        <v>1.060893664452496</v>
+        <v>0.8348215354643593</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.717346880444643</v>
+        <v>3.58170360305176</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-1.484343031978343</v>
+        <v>-1.839532068803535</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.486717044668059</v>
+        <v>2.344641429937982</v>
       </c>
       <c r="F1799" t="n">
-        <v>1.060893664452496</v>
+        <v>0.8348215354643593</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.717346880444643</v>
+        <v>3.58170360305176</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-1.256478349244832</v>
+        <v>-1.611667386070024</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.580079390868625</v>
+        <v>2.438003776138549</v>
       </c>
       <c r="F1800" t="n">
-        <v>1.060893664452496</v>
+        <v>0.8348215354643593</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.719563353551805</v>
+        <v>3.583920076158922</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-1.008376785377616</v>
+        <v>-1.363565822202807</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.686854612760604</v>
+        <v>2.544778998030528</v>
       </c>
       <c r="F1801" t="n">
-        <v>1.060893664452496</v>
+        <v>0.8348215354643593</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.727097949896897</v>
+        <v>3.591454672504014</v>
       </c>
     </row>
     <row r="1802">
@@ -42962,16 +42962,16 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-0.7115383859842852</v>
+        <v>-1.066727422809477</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.807012983491394</v>
+        <v>2.664937368761317</v>
       </c>
       <c r="F1802" t="n">
-        <v>1.175748152933624</v>
+        <v>0.949676023945487</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.797433653959031</v>
+        <v>3.661790376566149</v>
       </c>
     </row>
     <row r="1803">
@@ -42985,16 +42985,16 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-0.4078988291588487</v>
+        <v>-0.7630878659840402</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.930145880687255</v>
+        <v>2.788070265957178</v>
       </c>
       <c r="F1803" t="n">
-        <v>1.175748152933624</v>
+        <v>0.949676023945487</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.799110728424717</v>
+        <v>3.663467451031835</v>
       </c>
     </row>
     <row r="1804">
@@ -43008,16 +43008,16 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-0.1188782227181401</v>
+        <v>-0.4740672595433316</v>
       </c>
       <c r="E1804" t="n">
-        <v>3.041693544712996</v>
+        <v>2.899617929982919</v>
       </c>
       <c r="F1804" t="n">
-        <v>1.175748152933624</v>
+        <v>0.949676023945487</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.795050149874175</v>
+        <v>3.659406872481292</v>
       </c>
     </row>
     <row r="1805">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>0.1658417045457571</v>
+        <v>-0.1893473322794345</v>
       </c>
       <c r="E1805" t="n">
-        <v>3.160801654962572</v>
+        <v>3.018726040232496</v>
       </c>
       <c r="F1805" t="n">
-        <v>1.460468080197521</v>
+        <v>1.234395951209384</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.971102245576531</v>
+        <v>3.835458968183648</v>
       </c>
     </row>
     <row r="1806">
@@ -43054,16 +43054,16 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>0.4496033740372974</v>
+        <v>0.0944143372121059</v>
       </c>
       <c r="E1806" t="n">
-        <v>3.279618485932995</v>
+        <v>3.137542871202919</v>
       </c>
       <c r="F1806" t="n">
-        <v>1.460468080197521</v>
+        <v>1.234395951209384</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.976414408750338</v>
+        <v>3.840771131357455</v>
       </c>
     </row>
     <row r="1807">
@@ -43071,22 +43071,22 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>2.994653036913647</v>
+        <v>2.996521820962831</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>0.4511650853480568</v>
+        <v>0.3560627316047466</v>
       </c>
       <c r="E1807" t="n">
-        <v>3.273485757903932</v>
+        <v>3.235444816406609</v>
       </c>
       <c r="F1807" t="n">
-        <v>1.46202979150828</v>
+        <v>1.496044345602025</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.970594022983427</v>
+        <v>3.991002755439673</v>
       </c>
     </row>
   </sheetData>
